--- a/public/small_db_revised.xlsx
+++ b/public/small_db_revised.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hohi1\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hohi1\med_local\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7223F6-9919-4E09-812D-5D19C30A25D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D53D20-44C8-40FD-B6AD-2165B5091DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24570" yWindow="2085" windowWidth="21600" windowHeight="11055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
